--- a/data/trans_dic/ProbViv_estruc-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_estruc-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre)</t>
+          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre) (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,6; 18,33</t>
+          <t>7,69; 18,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,11; 9,9</t>
+          <t>3,06; 10,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,81; 12,24</t>
+          <t>6,11; 12,11</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,24; 9,85</t>
+          <t>4,32; 9,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,14; 14,25</t>
+          <t>7,16; 14,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,4; 11,0</t>
+          <t>6,43; 11,1</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,36; 15,97</t>
+          <t>5,29; 15,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,67; 14,12</t>
+          <t>5,43; 13,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,43; 13,3</t>
+          <t>6,34; 13,01</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,0; 17,43</t>
+          <t>7,43; 17,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,52; 17,5</t>
+          <t>8,39; 16,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,27; 15,65</t>
+          <t>9,53; 15,83</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,77; 12,4</t>
+          <t>7,72; 12,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,69; 11,81</t>
+          <t>7,82; 11,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,24; 11,28</t>
+          <t>8,24; 11,26</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre) (tasa de respuesta: 99,9%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>14049</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8440</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>22489</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>9024; 21175</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4298; 14213</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15742; 31217</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>12550</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>25219</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>37768</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>8184; 18831</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>18260; 35881</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>28578; 49353</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>18218</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17249</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>35467</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>10078; 29237</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10052; 25274</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>23832; 48886</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>19988</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>22422</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>42410</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>12486; 29798</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>15128; 30597</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>33203; 55123</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>64805</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>73329</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>138135</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>51383; 83388</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>59503; 88982</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>117506; 160601</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/ProbViv_estruc-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_estruc-Habitat-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,69; 18,05</t>
+          <t>7,81; 18,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,06; 10,12</t>
+          <t>3,07; 10,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,11; 12,11</t>
+          <t>6,14; 12,29</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,32; 9,94</t>
+          <t>4,16; 9,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,16; 14,07</t>
+          <t>6,7; 13,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,43; 11,1</t>
+          <t>6,39; 10,92</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,29; 15,36</t>
+          <t>5,4; 15,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,43; 13,64</t>
+          <t>5,82; 14,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,34; 13,01</t>
+          <t>6,76; 13,49</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,43; 17,74</t>
+          <t>7,93; 18,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,39; 16,97</t>
+          <t>8,69; 17,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,53; 15,83</t>
+          <t>8,95; 15,57</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,72; 12,54</t>
+          <t>7,62; 12,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,82; 11,69</t>
+          <t>7,63; 11,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,24; 11,26</t>
+          <t>8,22; 11,2</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9024; 21175</t>
+          <t>9154; 21470</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4298; 14213</t>
+          <t>4316; 14372</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15742; 31217</t>
+          <t>15812; 31675</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8184; 18831</t>
+          <t>7876; 18609</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18260; 35881</t>
+          <t>17088; 35434</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28578; 49353</t>
+          <t>28405; 48548</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10078; 29237</t>
+          <t>10291; 29548</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10052; 25274</t>
+          <t>10777; 26007</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23832; 48886</t>
+          <t>25410; 50676</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12486; 29798</t>
+          <t>13313; 30480</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15128; 30597</t>
+          <t>15673; 30723</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33203; 55123</t>
+          <t>31173; 54220</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>51383; 83388</t>
+          <t>50689; 81698</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>59503; 88982</t>
+          <t>58030; 90503</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>117506; 160601</t>
+          <t>117272; 159766</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/ProbViv_estruc-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_estruc-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,81; 18,31</t>
+          <t>2,99; 10,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,07; 10,24</t>
+          <t>7,96; 20,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,14; 12,29</t>
+          <t>6,19; 13,44</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,16; 9,82</t>
+          <t>7,51; 15,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,7; 13,89</t>
+          <t>4,52; 10,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,39; 10,92</t>
+          <t>6,68; 11,44</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,4; 15,52</t>
+          <t>5,41; 13,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,82; 14,04</t>
+          <t>6,18; 13,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,76; 13,49</t>
+          <t>6,78; 12,63</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,93; 18,15</t>
+          <t>8,46; 17,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,69; 17,04</t>
+          <t>7,02; 15,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,95; 15,57</t>
+          <t>8,77; 14,78</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,62; 12,28</t>
+          <t>7,84; 11,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,63; 11,89</t>
+          <t>7,92; 12,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,22; 11,2</t>
+          <t>8,45; 11,21</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14049</t>
+          <t>7600</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8440</t>
+          <t>15453</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22489</t>
+          <t>23053</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9154; 21470</t>
+          <t>3761; 12923</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4316; 14372</t>
+          <t>9636; 24664</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15812; 31675</t>
+          <t>15279; 33195</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>12550</t>
+          <t>24721</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>25219</t>
+          <t>12613</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37768</t>
+          <t>37335</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7876; 18609</t>
+          <t>17807; 35771</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17088; 35434</t>
+          <t>8284; 19072</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28405; 48548</t>
+          <t>28084; 48107</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18218</t>
+          <t>14941</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17249</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35467</t>
+          <t>30394</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10291; 29548</t>
+          <t>9100; 23052</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10777; 26007</t>
+          <t>9713; 21829</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25410; 50676</t>
+          <t>22062; 41102</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>19988</t>
+          <t>20922</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>22422</t>
+          <t>17836</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42410</t>
+          <t>38758</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13313; 30480</t>
+          <t>14254; 29402</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15673; 30723</t>
+          <t>11735; 25690</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31173; 54220</t>
+          <t>29431; 49605</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>94</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>64805</t>
+          <t>68184</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>73329</t>
+          <t>61356</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>138135</t>
+          <t>129540</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>50689; 81698</t>
+          <t>54905; 83074</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>58030; 90503</t>
+          <t>49795; 75604</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>117272; 159766</t>
+          <t>112229; 148939</t>
         </is>
       </c>
     </row>
